--- a/Slides/data/Aula-Pratica-AAS-Planilha-Analise-Semiautomatica-Exemplo-Sanquetta-et-al-2023.xlsx
+++ b/Slides/data/Aula-Pratica-AAS-Planilha-Analise-Semiautomatica-Exemplo-Sanquetta-et-al-2023.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/37cd5d8700b5386d/GitHub/FL03039-Inventario-Florestal/Slides/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{FBDD67E5-22CB-4132-A16F-019A20304AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4997762-07D9-46C8-BF26-91E2A5195C79}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{FBDD67E5-22CB-4132-A16F-019A20304AAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A96A43EE-0A50-40A0-A708-630B23628D57}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -850,13 +850,13 @@
       <xdr:col>4</xdr:col>
       <xdr:colOff>374196</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>164419</xdr:rowOff>
+      <xdr:rowOff>164420</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>2613704</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>79374</xdr:rowOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>158751</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -871,8 +871,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4756830" y="6588124"/>
-          <a:ext cx="9400267" cy="2029732"/>
+          <a:off x="4756830" y="6616474"/>
+          <a:ext cx="9400267" cy="1751920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
